--- a/data/trans_orig/IP26C_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP26C_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2007 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2007 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19782</t>
+          <t>20491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31848</t>
+          <t>33084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83908</t>
+          <t>83199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94808</t>
+          <t>94906</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81560</t>
+          <t>81660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91609</t>
+          <t>91536</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>169387</t>
+          <t>168151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>184044</t>
+          <t>184099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14017</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19792</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72749</t>
+          <t>73479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82485</t>
+          <t>82213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75535</t>
+          <t>75789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>82696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152250</t>
+          <t>152077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>163672</t>
+          <t>163204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>30542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51665</t>
+          <t>52766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61690</t>
+          <t>61524</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79639</t>
+          <t>80099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90339</t>
+          <t>90701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135948</t>
+          <t>135474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149665</t>
+          <t>149729</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34111</t>
+          <t>35281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53813</t>
+          <t>54473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173809</t>
+          <t>174592</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187432</t>
+          <t>187593</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168488</t>
+          <t>167614</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182858</t>
+          <t>182674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>347030</t>
+          <t>346370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366732</t>
+          <t>365562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>19688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26910</t>
+          <t>26469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85005</t>
+          <t>84432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96076</t>
+          <t>96206</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>114132</t>
+          <t>113639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122539</t>
+          <t>122516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202477</t>
+          <t>202918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216771</t>
+          <t>216840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23992</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57306</t>
+          <t>56962</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67122</t>
+          <t>67170</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62474</t>
+          <t>62454</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69731</t>
+          <t>69769</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122616</t>
+          <t>122778</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135463</t>
+          <t>135570</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61988</t>
+          <t>62679</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88865</t>
+          <t>88342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53050</t>
+          <t>52880</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76743</t>
+          <t>76195</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121070</t>
+          <t>120642</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156692</t>
+          <t>156378</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>548000</t>
+          <t>548523</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>574877</t>
+          <t>574186</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>602524</t>
+          <t>603072</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>626217</t>
+          <t>626387</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1159440</t>
+          <t>1159754</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1195062</t>
+          <t>1195490</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2012 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2012 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13997</t>
+          <t>13587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22010</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77383</t>
+          <t>77689</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85263</t>
+          <t>85490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75138</t>
+          <t>75548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83990</t>
+          <t>84074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155204</t>
+          <t>155824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167720</t>
+          <t>167890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30375</t>
+          <t>30663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73416</t>
+          <t>72578</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84145</t>
+          <t>83768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80119</t>
+          <t>79919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90582</t>
+          <t>90176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157559</t>
+          <t>157271</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171792</t>
+          <t>171776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71345</t>
+          <t>71648</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81055</t>
+          <t>81288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71069</t>
+          <t>71498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80385</t>
+          <t>80463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146716</t>
+          <t>146578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159717</t>
+          <t>159924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24500</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>30817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49958</t>
+          <t>49175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180236</t>
+          <t>180242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194361</t>
+          <t>193968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193110</t>
+          <t>193240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207818</t>
+          <t>208152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378835</t>
+          <t>379618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>398475</t>
+          <t>398595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23321</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24278</t>
+          <t>24422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45314</t>
+          <t>43054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123462</t>
+          <t>122397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136253</t>
+          <t>135950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115481</t>
+          <t>115337</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128628</t>
+          <t>128185</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>241228</t>
+          <t>243488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259982</t>
+          <t>261218</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14994</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,47 +5098,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>29,4%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>12436</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7358</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>18387</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>28,2%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>12436</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>7757</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>18988</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30611</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38183</t>
+          <t>37542</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47848</t>
+          <t>47439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,49 +5211,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>60974</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>55023</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>66052</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>83,06%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>74,95%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>89,98%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>60974</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>54422</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>65653</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>74,13%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>150</t>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95976</t>
+          <t>96050</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110349</t>
+          <t>110456</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56381</t>
+          <t>57984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82514</t>
+          <t>84740</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66975</t>
+          <t>66099</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94759</t>
+          <t>93379</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130362</t>
+          <t>130854</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168904</t>
+          <t>169797</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>588215</t>
+          <t>585989</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614348</t>
+          <t>612745</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>613342</t>
+          <t>614722</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>641126</t>
+          <t>642002</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1209926</t>
+          <t>1209033</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1248468</t>
+          <t>1247976</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2016 (tasa de respuesta: 99,01%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2016 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12410</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23577</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69954</t>
+          <t>69696</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78059</t>
+          <t>78225</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85668</t>
+          <t>85662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95153</t>
+          <t>95008</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158584</t>
+          <t>158762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171316</t>
+          <t>171382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>26522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88963</t>
+          <t>89256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98375</t>
+          <t>98864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95420</t>
+          <t>96140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105977</t>
+          <t>106287</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188840</t>
+          <t>189353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>202572</t>
+          <t>202890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59237</t>
+          <t>59316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60952</t>
+          <t>60026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69925</t>
+          <t>70063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115429</t>
+          <t>115610</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127469</t>
+          <t>127488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30478</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>28325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33878</t>
+          <t>33113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53480</t>
+          <t>52904</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188839</t>
+          <t>188140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203567</t>
+          <t>203095</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181286</t>
+          <t>180536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>194577</t>
+          <t>193892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>374698</t>
+          <t>375274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>394300</t>
+          <t>395065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15048</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>29599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119818</t>
+          <t>119368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129800</t>
+          <t>129955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123760</t>
+          <t>123592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134759</t>
+          <t>134653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247908</t>
+          <t>248134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262200</t>
+          <t>262685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>48650</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57435</t>
+          <t>57534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56178</t>
+          <t>57554</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64695</t>
+          <t>64365</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109959</t>
+          <t>110380</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>121167</t>
+          <t>120962</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49984</t>
+          <t>51200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75554</t>
+          <t>74894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51149</t>
+          <t>51876</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76085</t>
+          <t>76703</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109329</t>
+          <t>107931</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>145069</t>
+          <t>142767</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>589150</t>
+          <t>589810</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614720</t>
+          <t>613504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>627354</t>
+          <t>626736</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>652290</t>
+          <t>651563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1223074</t>
+          <t>1225376</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1258814</t>
+          <t>1260212</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>26051</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37173</t>
+          <t>37138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89602</t>
+          <t>89601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98460</t>
+          <t>98610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109017</t>
+          <t>110857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125056</t>
+          <t>125279</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>203007</t>
+          <t>203042</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>220687</t>
+          <t>220639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14699</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79982</t>
+          <t>79932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89823</t>
+          <t>89336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80321</t>
+          <t>80765</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90383</t>
+          <t>90187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164151</t>
+          <t>164170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177546</t>
+          <t>177793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22309</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>42732</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50074</t>
+          <t>50078</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46553</t>
+          <t>47372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57379</t>
+          <t>57648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93405</t>
+          <t>92772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>106067</t>
+          <t>105639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25693</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22953</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192317</t>
+          <t>192371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207941</t>
+          <t>207669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195697</t>
+          <t>196365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209314</t>
+          <t>208794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>392785</t>
+          <t>393889</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>413329</t>
+          <t>412808</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24893</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42923</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95725</t>
+          <t>96247</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108627</t>
+          <t>108802</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137724</t>
+          <t>137559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153010</t>
+          <t>152468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>239122</t>
+          <t>238973</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258455</t>
+          <t>259069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>20377</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>61875</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67458</t>
+          <t>67305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51179</t>
+          <t>51626</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64724</t>
+          <t>64450</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116056</t>
+          <t>115612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>130299</t>
+          <t>130045</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46763</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73240</t>
+          <t>71917</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68205</t>
+          <t>66933</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99669</t>
+          <t>97390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122851</t>
+          <t>122498</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>162314</t>
+          <t>162693</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>582907</t>
+          <t>584230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609384</t>
+          <t>609086</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>649556</t>
+          <t>651835</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681020</t>
+          <t>682292</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1243059</t>
+          <t>1242680</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1282522</t>
+          <t>1282875</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
